--- a/令和9年度_授業数カウント（案）.xlsx
+++ b/令和9年度_授業数カウント（案）.xlsx
@@ -10,7 +10,8 @@
   <sheets>
     <sheet name="授業数カウント" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="区切り別集計" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="作り方" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="2年 総合→道徳・学活" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="作り方" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,8 +22,298 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="M95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに道徳</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P47" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに道徳</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P67" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P81" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに道徳</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P117" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに道徳</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P127" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P143" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに道徳</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P159" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P167" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに道徳</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P182" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P197" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年は総合のかわりに学活</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3350" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3385" uniqueCount="329">
   <si>
     <r>
       <rPr>
@@ -4543,10 +4834,20 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">令和</t>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年：総合のコマ（火</t>
     </r>
     <r>
       <rPr>
@@ -4556,7 +4857,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -4565,21 +4866,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年度 授業数カウントの作り方</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">・年計の行事から、毎日・学年ごとに授業ができる時限を出し、どの曜日の何限の時間割を行うかを割り振った。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・条件</t>
+      <t xml:space="preserve">・金</t>
     </r>
     <r>
       <rPr>
@@ -4589,7 +4876,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -4598,7 +4885,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：確認テスト・</t>
+      <t xml:space="preserve">）を道徳・学活に入れ替える日（年</t>
     </r>
     <r>
       <rPr>
@@ -4608,7 +4895,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">14</t>
     </r>
     <r>
       <rPr>
@@ -4617,7 +4904,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">学期期末・中間・</t>
+      <t xml:space="preserve">回：学活</t>
     </r>
     <r>
       <rPr>
@@ -4627,7 +4914,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">8</t>
     </r>
     <r>
       <rPr>
@@ -4636,7 +4923,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">学期期末・学年末テストの区切りごとに、各コマの回数の差を</t>
+      <t xml:space="preserve">・道徳</t>
     </r>
     <r>
       <rPr>
@@ -4646,7 +4933,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -4655,8 +4942,29 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">以内にする。</t>
-    </r>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">時限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">もとのコマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入れ替え後</t>
+  </si>
+  <si>
+    <t xml:space="preserve">火６（総合）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">学活</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金６（総合）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道徳</t>
   </si>
   <si>
     <r>
@@ -4666,7 +4974,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・条件</t>
+      <t xml:space="preserve">令和</t>
     </r>
     <r>
       <rPr>
@@ -4676,7 +4984,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">9</t>
     </r>
     <r>
       <rPr>
@@ -4685,7 +4993,21 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：</t>
+      <t xml:space="preserve">年度 授業数カウントの作り方</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・年計の行事から、毎日・学年ごとに授業ができる時限を出し、どの曜日の何限の時間割を行うかを割り振った。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・条件</t>
     </r>
     <r>
       <rPr>
@@ -4704,7 +5026,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">限には、どこかの曜日の</t>
+      <t xml:space="preserve">：確認テスト・</t>
     </r>
     <r>
       <rPr>
@@ -4723,7 +5045,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">限か、</t>
+      <t xml:space="preserve">学期期末・中間・</t>
     </r>
     <r>
       <rPr>
@@ -4733,7 +5055,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -4742,7 +5064,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">限の道徳・学活・総合（月</t>
+      <t xml:space="preserve">学期期末・学年末テストの区切りごとに、各コマの回数の差を</t>
     </r>
     <r>
       <rPr>
@@ -4752,7 +5074,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -4761,7 +5083,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・水</t>
+      <t xml:space="preserve">以内にする。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・条件</t>
     </r>
     <r>
       <rPr>
@@ -4771,7 +5104,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -4780,7 +5113,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・金</t>
+      <t xml:space="preserve">：</t>
     </r>
     <r>
       <rPr>
@@ -4790,7 +5123,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -4799,7 +5132,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）だけを置く（</t>
+      <t xml:space="preserve">限には、どこかの曜日の</t>
     </r>
     <r>
       <rPr>
@@ -4809,7 +5142,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -4818,7 +5151,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">限を</t>
+      <t xml:space="preserve">限か、</t>
     </r>
     <r>
       <rPr>
@@ -4828,7 +5161,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -4837,18 +5170,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">限に繰り上げない）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・条件</t>
+      <t xml:space="preserve">限の道徳・学活・総合（月</t>
     </r>
     <r>
       <rPr>
@@ -4858,7 +5180,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -4867,7 +5189,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：</t>
+      <t xml:space="preserve">・水</t>
     </r>
     <r>
       <rPr>
@@ -4877,7 +5199,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -4886,7 +5208,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日に使う曜日は</t>
+      <t xml:space="preserve">・金</t>
     </r>
     <r>
       <rPr>
@@ -4896,7 +5218,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -4905,21 +5227,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">つまで。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">・各時限は、全学年同じ曜日・時限を行う（先生の重なりを防ぐため）。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・結果：</t>
+      <t xml:space="preserve">）だけを置く（</t>
     </r>
     <r>
       <rPr>
@@ -4929,7 +5237,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -4938,7 +5246,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年の「</t>
+      <t xml:space="preserve">限を</t>
     </r>
     <r>
       <rPr>
@@ -4948,7 +5256,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -4957,7 +5265,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">学期期末後〜学年末」だけ差</t>
+      <t xml:space="preserve">限に繰り上げない）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・条件</t>
     </r>
     <r>
       <rPr>
@@ -4976,7 +5295,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。ほかはすべて差</t>
+      <t xml:space="preserve">：</t>
     </r>
     <r>
       <rPr>
@@ -4986,7 +5305,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -4995,7 +5314,233 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">日に使う曜日は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つまで。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・各時限は、全学年同じ曜日・時限を行う（先生の重なりを防ぐため）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・結果：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年の「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">学期期末後〜学年末」だけ差</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。ほかはすべて差</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">以内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・水色＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年の総合を道徳・学活に入れ替えるコマ（「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年 総合→道徳・学活」シート）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年の道徳・学活、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年の美術・技家の不足分は、来年度の時間割ができてから差し替え表を作る（やること</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
     </r>
   </si>
 </sst>
@@ -5007,7 +5552,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5060,8 +5605,18 @@
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5071,7 +5626,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE6F0"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -5084,6 +5639,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFDDE6F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -5136,7 +5697,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5169,6 +5730,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
@@ -5191,6 +5756,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5223,7 +5792,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFDDE6F0"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -5237,7 +5806,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFDDE6F0"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -5782,7 +6351,7 @@
       <c r="O8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="8" t="s">
         <v>53</v>
       </c>
       <c r="Q8" s="7" t="s">
@@ -6550,7 +7119,7 @@
       <c r="O20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P20" s="5" t="s">
+      <c r="P20" s="8" t="s">
         <v>56</v>
       </c>
       <c r="Q20" s="5" t="s">
@@ -7392,7 +7961,7 @@
       <c r="O34" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="P34" s="5" t="s">
+      <c r="P34" s="8" t="s">
         <v>53</v>
       </c>
       <c r="Q34" s="5" t="s">
@@ -8138,7 +8707,7 @@
       <c r="O47" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P47" s="5" t="s">
+      <c r="P47" s="8" t="s">
         <v>56</v>
       </c>
       <c r="Q47" s="6"/>
@@ -9274,7 +9843,7 @@
       <c r="O67" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P67" s="5" t="s">
+      <c r="P67" s="8" t="s">
         <v>56</v>
       </c>
       <c r="Q67" s="5" t="s">
@@ -10074,7 +10643,7 @@
       <c r="O81" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P81" s="7" t="s">
+      <c r="P81" s="8" t="s">
         <v>53</v>
       </c>
       <c r="Q81" s="5" t="s">
@@ -10883,7 +11452,7 @@
       <c r="L95" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="M95" s="7" t="s">
+      <c r="M95" s="8" t="s">
         <v>56</v>
       </c>
       <c r="N95" s="5" t="s">
@@ -12152,7 +12721,7 @@
       <c r="O117" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P117" s="5" t="s">
+      <c r="P117" s="8" t="s">
         <v>56</v>
       </c>
       <c r="Q117" s="7" t="s">
@@ -12702,7 +13271,7 @@
       <c r="O127" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P127" s="5" t="s">
+      <c r="P127" s="8" t="s">
         <v>56</v>
       </c>
       <c r="Q127" s="6"/>
@@ -13694,7 +14263,7 @@
       <c r="O143" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="P143" s="7" t="s">
+      <c r="P143" s="8" t="s">
         <v>53</v>
       </c>
       <c r="Q143" s="7" t="s">
@@ -14630,7 +15199,7 @@
       <c r="O159" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P159" s="5" t="s">
+      <c r="P159" s="8" t="s">
         <v>56</v>
       </c>
       <c r="Q159" s="5" t="s">
@@ -14709,7 +15278,7 @@
       <c r="B161" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C161" s="8" t="s">
+      <c r="C161" s="9" t="s">
         <v>242</v>
       </c>
       <c r="D161" s="5" t="s">
@@ -15140,7 +15709,7 @@
       <c r="O167" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="P167" s="7" t="s">
+      <c r="P167" s="8" t="s">
         <v>56</v>
       </c>
       <c r="Q167" s="5" t="s">
@@ -15627,7 +16196,7 @@
       <c r="B175" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="9" t="s">
         <v>261</v>
       </c>
       <c r="D175" s="5" t="s">
@@ -15981,7 +16550,7 @@
       <c r="B181" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="C181" s="9" t="s">
         <v>269</v>
       </c>
       <c r="D181" s="5" t="s">
@@ -16043,7 +16612,7 @@
       <c r="B182" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C182" s="9" t="s">
+      <c r="C182" s="10" t="s">
         <v>271</v>
       </c>
       <c r="D182" s="5" t="s">
@@ -16082,7 +16651,7 @@
       <c r="O182" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P182" s="7" t="s">
+      <c r="P182" s="8" t="s">
         <v>53</v>
       </c>
       <c r="Q182" s="5" t="s">
@@ -16111,7 +16680,7 @@
       <c r="B183" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C183" s="9" t="s">
+      <c r="C183" s="10" t="s">
         <v>273</v>
       </c>
       <c r="D183" s="5" t="s">
@@ -16167,7 +16736,7 @@
       <c r="B184" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C184" s="9" t="s">
+      <c r="C184" s="10" t="s">
         <v>275</v>
       </c>
       <c r="D184" s="5" t="s">
@@ -16223,7 +16792,7 @@
       <c r="B185" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C185" s="9"/>
+      <c r="C185" s="10"/>
       <c r="D185" s="5" t="s">
         <v>277</v>
       </c>
@@ -16285,7 +16854,7 @@
       <c r="B186" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C186" s="9"/>
+      <c r="C186" s="10"/>
       <c r="D186" s="5" t="s">
         <v>218</v>
       </c>
@@ -16302,7 +16871,7 @@
         <v>36</v>
       </c>
       <c r="I186" s="6"/>
-      <c r="J186" s="9"/>
+      <c r="J186" s="10"/>
       <c r="K186" s="5" t="s">
         <v>61</v>
       </c>
@@ -16312,7 +16881,7 @@
         <v>36</v>
       </c>
       <c r="O186" s="6"/>
-      <c r="P186" s="9"/>
+      <c r="P186" s="10"/>
       <c r="Q186" s="5" t="s">
         <v>61</v>
       </c>
@@ -16328,7 +16897,7 @@
       <c r="U186" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="V186" s="9"/>
+      <c r="V186" s="10"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="n">
@@ -16337,7 +16906,7 @@
       <c r="B187" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C187" s="9" t="s">
+      <c r="C187" s="10" t="s">
         <v>278</v>
       </c>
       <c r="D187" s="5" t="s">
@@ -16527,12 +17096,12 @@
       <c r="P190" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="Q190" s="9"/>
-      <c r="R190" s="9"/>
-      <c r="S190" s="9"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
+      <c r="Q190" s="10"/>
+      <c r="R190" s="10"/>
+      <c r="S190" s="10"/>
+      <c r="T190" s="10"/>
+      <c r="U190" s="10"/>
+      <c r="V190" s="10"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="n">
@@ -16562,7 +17131,7 @@
       <c r="I191" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J191" s="9"/>
+      <c r="J191" s="10"/>
       <c r="K191" s="7" t="s">
         <v>79</v>
       </c>
@@ -16578,13 +17147,13 @@
       <c r="O191" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="P191" s="9"/>
-      <c r="Q191" s="9"/>
-      <c r="R191" s="9"/>
-      <c r="S191" s="9"/>
-      <c r="T191" s="9"/>
-      <c r="U191" s="9"/>
-      <c r="V191" s="9"/>
+      <c r="P191" s="10"/>
+      <c r="Q191" s="10"/>
+      <c r="R191" s="10"/>
+      <c r="S191" s="10"/>
+      <c r="T191" s="10"/>
+      <c r="U191" s="10"/>
+      <c r="V191" s="10"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="n">
@@ -16593,7 +17162,7 @@
       <c r="B192" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C192" s="9"/>
+      <c r="C192" s="10"/>
       <c r="D192" s="5" t="s">
         <v>286</v>
       </c>
@@ -16625,12 +17194,12 @@
       </c>
       <c r="O192" s="6"/>
       <c r="P192" s="6"/>
-      <c r="Q192" s="9"/>
-      <c r="R192" s="9"/>
-      <c r="S192" s="9"/>
-      <c r="T192" s="9"/>
-      <c r="U192" s="9"/>
-      <c r="V192" s="9"/>
+      <c r="Q192" s="10"/>
+      <c r="R192" s="10"/>
+      <c r="S192" s="10"/>
+      <c r="T192" s="10"/>
+      <c r="U192" s="10"/>
+      <c r="V192" s="10"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="n">
@@ -16677,12 +17246,12 @@
         <v>65</v>
       </c>
       <c r="P193" s="6"/>
-      <c r="Q193" s="9"/>
-      <c r="R193" s="9"/>
-      <c r="S193" s="9"/>
-      <c r="T193" s="9"/>
-      <c r="U193" s="9"/>
-      <c r="V193" s="9"/>
+      <c r="Q193" s="10"/>
+      <c r="R193" s="10"/>
+      <c r="S193" s="10"/>
+      <c r="T193" s="10"/>
+      <c r="U193" s="10"/>
+      <c r="V193" s="10"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="n">
@@ -16691,7 +17260,7 @@
       <c r="B194" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C194" s="9" t="s">
+      <c r="C194" s="10" t="s">
         <v>288</v>
       </c>
       <c r="D194" s="5" t="s">
@@ -16733,12 +17302,12 @@
       <c r="P194" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="Q194" s="9"/>
-      <c r="R194" s="9"/>
-      <c r="S194" s="9"/>
-      <c r="T194" s="9"/>
-      <c r="U194" s="9"/>
-      <c r="V194" s="9"/>
+      <c r="Q194" s="10"/>
+      <c r="R194" s="10"/>
+      <c r="S194" s="10"/>
+      <c r="T194" s="10"/>
+      <c r="U194" s="10"/>
+      <c r="V194" s="10"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="n">
@@ -16789,12 +17358,12 @@
       <c r="P195" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="Q195" s="9"/>
-      <c r="R195" s="9"/>
-      <c r="S195" s="9"/>
-      <c r="T195" s="9"/>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
+      <c r="Q195" s="10"/>
+      <c r="R195" s="10"/>
+      <c r="S195" s="10"/>
+      <c r="T195" s="10"/>
+      <c r="U195" s="10"/>
+      <c r="V195" s="10"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4" t="n">
@@ -16803,7 +17372,7 @@
       <c r="B196" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C196" s="9" t="s">
+      <c r="C196" s="10" t="s">
         <v>291</v>
       </c>
       <c r="D196" s="5" t="s">
@@ -16822,7 +17391,7 @@
         <v>36</v>
       </c>
       <c r="I196" s="6"/>
-      <c r="J196" s="9"/>
+      <c r="J196" s="10"/>
       <c r="K196" s="5" t="s">
         <v>61</v>
       </c>
@@ -16836,13 +17405,13 @@
         <v>36</v>
       </c>
       <c r="O196" s="6"/>
-      <c r="P196" s="9"/>
-      <c r="Q196" s="9"/>
-      <c r="R196" s="9"/>
-      <c r="S196" s="9"/>
-      <c r="T196" s="9"/>
-      <c r="U196" s="9"/>
-      <c r="V196" s="9"/>
+      <c r="P196" s="10"/>
+      <c r="Q196" s="10"/>
+      <c r="R196" s="10"/>
+      <c r="S196" s="10"/>
+      <c r="T196" s="10"/>
+      <c r="U196" s="10"/>
+      <c r="V196" s="10"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="n">
@@ -16851,7 +17420,7 @@
       <c r="B197" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C197" s="9"/>
+      <c r="C197" s="10"/>
       <c r="D197" s="5" t="s">
         <v>78</v>
       </c>
@@ -16888,15 +17457,15 @@
       <c r="O197" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P197" s="5" t="s">
+      <c r="P197" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="Q197" s="9"/>
-      <c r="R197" s="9"/>
-      <c r="S197" s="9"/>
-      <c r="T197" s="9"/>
-      <c r="U197" s="9"/>
-      <c r="V197" s="9"/>
+      <c r="Q197" s="10"/>
+      <c r="R197" s="10"/>
+      <c r="S197" s="10"/>
+      <c r="T197" s="10"/>
+      <c r="U197" s="10"/>
+      <c r="V197" s="10"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="n">
@@ -16947,12 +17516,12 @@
       <c r="P198" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Q198" s="9"/>
-      <c r="R198" s="9"/>
-      <c r="S198" s="9"/>
-      <c r="T198" s="9"/>
-      <c r="U198" s="9"/>
-      <c r="V198" s="9"/>
+      <c r="Q198" s="10"/>
+      <c r="R198" s="10"/>
+      <c r="S198" s="10"/>
+      <c r="T198" s="10"/>
+      <c r="U198" s="10"/>
+      <c r="V198" s="10"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="n">
@@ -16961,7 +17530,7 @@
       <c r="B199" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C199" s="9"/>
+      <c r="C199" s="10"/>
       <c r="D199" s="5" t="s">
         <v>294</v>
       </c>
@@ -17001,12 +17570,12 @@
       <c r="P199" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="Q199" s="9"/>
-      <c r="R199" s="9"/>
-      <c r="S199" s="9"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
+      <c r="Q199" s="10"/>
+      <c r="R199" s="10"/>
+      <c r="S199" s="10"/>
+      <c r="T199" s="10"/>
+      <c r="U199" s="10"/>
+      <c r="V199" s="10"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="n">
@@ -17034,7 +17603,7 @@
         <v>36</v>
       </c>
       <c r="I200" s="6"/>
-      <c r="J200" s="9"/>
+      <c r="J200" s="10"/>
       <c r="K200" s="5" t="s">
         <v>61</v>
       </c>
@@ -17048,13 +17617,13 @@
       <c r="O200" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P200" s="9"/>
-      <c r="Q200" s="9"/>
-      <c r="R200" s="9"/>
-      <c r="S200" s="9"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
+      <c r="P200" s="10"/>
+      <c r="Q200" s="10"/>
+      <c r="R200" s="10"/>
+      <c r="S200" s="10"/>
+      <c r="T200" s="10"/>
+      <c r="U200" s="10"/>
+      <c r="V200" s="10"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="n">
@@ -17085,12 +17654,12 @@
       <c r="N201" s="6"/>
       <c r="O201" s="6"/>
       <c r="P201" s="6"/>
-      <c r="Q201" s="9"/>
-      <c r="R201" s="9"/>
-      <c r="S201" s="9"/>
-      <c r="T201" s="9"/>
-      <c r="U201" s="9"/>
-      <c r="V201" s="9"/>
+      <c r="Q201" s="10"/>
+      <c r="R201" s="10"/>
+      <c r="S201" s="10"/>
+      <c r="T201" s="10"/>
+      <c r="U201" s="10"/>
+      <c r="V201" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -17100,6 +17669,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -17121,3112 +17691,3112 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="T4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="U4" s="11" t="s">
+      <c r="U4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="11" t="s">
+      <c r="V4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W4" s="11" t="s">
+      <c r="W4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="X4" s="11" t="s">
+      <c r="X4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" s="11" t="s">
+      <c r="Y4" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="Z4" s="11" t="s">
+      <c r="Z4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AA4" s="11" t="s">
+      <c r="AA4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="AB4" s="11" t="s">
+      <c r="AB4" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AC4" s="11" t="s">
+      <c r="AC4" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="AD4" s="11" t="s">
+      <c r="AD4" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="AE4" s="11" t="s">
+      <c r="AE4" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="AF4" s="11" t="s">
+      <c r="AF4" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="AG4" s="11" t="s">
+      <c r="AG4" s="12" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="月１"))</f>
         <v>5</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="月２"))</f>
         <v>5</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="月４"))</f>
         <v>5</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="月５"))</f>
         <v>4</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="月６"))</f>
         <v>4</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="火１"))</f>
         <v>4</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="火２"))</f>
         <v>4</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="火３"))</f>
         <v>5</v>
       </c>
-      <c r="K5" s="12" t="n">
+      <c r="K5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="火４"))</f>
         <v>5</v>
       </c>
-      <c r="L5" s="12" t="n">
+      <c r="L5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="火５"))</f>
         <v>4</v>
       </c>
-      <c r="M5" s="12" t="n">
+      <c r="M5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="火６"))</f>
         <v>4</v>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="N5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="水１"))</f>
         <v>4</v>
       </c>
-      <c r="O5" s="12" t="n">
+      <c r="O5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="水２"))</f>
         <v>4</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="水３"))</f>
         <v>4</v>
       </c>
-      <c r="Q5" s="12" t="n">
+      <c r="Q5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="水４"))</f>
         <v>4</v>
       </c>
-      <c r="R5" s="12" t="n">
+      <c r="R5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="水５"))</f>
         <v>4</v>
       </c>
-      <c r="S5" s="12" t="n">
+      <c r="S5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="水６"))</f>
         <v>4</v>
       </c>
-      <c r="T5" s="12" t="n">
+      <c r="T5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="木１"))</f>
         <v>4</v>
       </c>
-      <c r="U5" s="12" t="n">
+      <c r="U5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="木２"))</f>
         <v>4</v>
       </c>
-      <c r="V5" s="12" t="n">
+      <c r="V5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="木３"))</f>
         <v>5</v>
       </c>
-      <c r="W5" s="12" t="n">
+      <c r="W5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="木４"))</f>
         <v>5</v>
       </c>
-      <c r="X5" s="12" t="n">
+      <c r="X5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y5" s="12" t="n">
+      <c r="Y5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="金１"))</f>
         <v>4</v>
       </c>
-      <c r="Z5" s="12" t="n">
+      <c r="Z5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="金２"))</f>
         <v>3</v>
       </c>
-      <c r="AA5" s="12" t="n">
+      <c r="AA5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="金３"))</f>
         <v>4</v>
       </c>
-      <c r="AB5" s="12" t="n">
+      <c r="AB5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="金４"))</f>
         <v>4</v>
       </c>
-      <c r="AC5" s="12" t="n">
+      <c r="AC5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="金５"))</f>
         <v>5</v>
       </c>
-      <c r="AD5" s="12" t="n">
+      <c r="AD5" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$E$3:$J$201="金６"))</f>
         <v>5</v>
       </c>
-      <c r="AE5" s="12" t="n">
+      <c r="AE5" s="13" t="n">
         <f aca="false">MIN(B5:AD5)</f>
         <v>3</v>
       </c>
-      <c r="AF5" s="12" t="n">
+      <c r="AF5" s="13" t="n">
         <f aca="false">MAX(B5:AD5)</f>
         <v>5</v>
       </c>
-      <c r="AG5" s="12" t="n">
+      <c r="AG5" s="13" t="n">
         <f aca="false">AF5-AE5</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="月１"))</f>
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="月２"))</f>
         <v>4</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="月４"))</f>
         <v>4</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="月５"))</f>
         <v>4</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="月６"))</f>
         <v>5</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="火１"))</f>
         <v>5</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="火３"))</f>
         <v>4</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="火４"))</f>
         <v>4</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="火５"))</f>
         <v>4</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="火６"))</f>
         <v>5</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O6" s="12" t="n">
+      <c r="O6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="水２"))</f>
         <v>5</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="水３"))</f>
         <v>5</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="水５"))</f>
         <v>4</v>
       </c>
-      <c r="S6" s="12" t="n">
+      <c r="S6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="水６"))</f>
         <v>5</v>
       </c>
-      <c r="T6" s="12" t="n">
+      <c r="T6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="木１"))</f>
         <v>5</v>
       </c>
-      <c r="U6" s="12" t="n">
+      <c r="U6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="木２"))</f>
         <v>5</v>
       </c>
-      <c r="V6" s="12" t="n">
+      <c r="V6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="木３"))</f>
         <v>5</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="木４"))</f>
         <v>5</v>
       </c>
-      <c r="X6" s="12" t="n">
+      <c r="X6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="木５"))</f>
         <v>5</v>
       </c>
-      <c r="Y6" s="12" t="n">
+      <c r="Y6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="金１"))</f>
         <v>5</v>
       </c>
-      <c r="Z6" s="12" t="n">
+      <c r="Z6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="金２"))</f>
         <v>5</v>
       </c>
-      <c r="AA6" s="12" t="n">
+      <c r="AA6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="金３"))</f>
         <v>5</v>
       </c>
-      <c r="AB6" s="12" t="n">
+      <c r="AB6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC6" s="12" t="n">
+      <c r="AC6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="金５"))</f>
         <v>4</v>
       </c>
-      <c r="AD6" s="12" t="n">
+      <c r="AD6" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$E$3:$J$201="金６"))</f>
         <v>5</v>
       </c>
-      <c r="AE6" s="12" t="n">
+      <c r="AE6" s="13" t="n">
         <f aca="false">MIN(B6:AD6)</f>
         <v>4</v>
       </c>
-      <c r="AF6" s="12" t="n">
+      <c r="AF6" s="13" t="n">
         <f aca="false">MAX(B6:AD6)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="12" t="n">
+      <c r="AG6" s="13" t="n">
         <f aca="false">AF6-AE6</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="月１"))</f>
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="月２"))</f>
         <v>6</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="月４"))</f>
         <v>6</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="月５"))</f>
         <v>5</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="月６"))</f>
         <v>6</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="火１"))</f>
         <v>5</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="火３"))</f>
         <v>6</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="火４"))</f>
         <v>5</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="火５"))</f>
         <v>5</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="火６"))</f>
         <v>6</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="水２"))</f>
         <v>6</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="水３"))</f>
         <v>6</v>
       </c>
-      <c r="Q7" s="12" t="n">
+      <c r="Q7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R7" s="12" t="n">
+      <c r="R7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="水５"))</f>
         <v>5</v>
       </c>
-      <c r="S7" s="12" t="n">
+      <c r="S7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="水６"))</f>
         <v>6</v>
       </c>
-      <c r="T7" s="12" t="n">
+      <c r="T7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="木１"))</f>
         <v>6</v>
       </c>
-      <c r="U7" s="12" t="n">
+      <c r="U7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="木２"))</f>
         <v>5</v>
       </c>
-      <c r="V7" s="12" t="n">
+      <c r="V7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="木３"))</f>
         <v>5</v>
       </c>
-      <c r="W7" s="12" t="n">
+      <c r="W7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="木４"))</f>
         <v>6</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y7" s="12" t="n">
+      <c r="Y7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="金１"))</f>
         <v>6</v>
       </c>
-      <c r="Z7" s="12" t="n">
+      <c r="Z7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="金２"))</f>
         <v>5</v>
       </c>
-      <c r="AA7" s="12" t="n">
+      <c r="AA7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="金３"))</f>
         <v>5</v>
       </c>
-      <c r="AB7" s="12" t="n">
+      <c r="AB7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC7" s="12" t="n">
+      <c r="AC7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="金５"))</f>
         <v>4</v>
       </c>
-      <c r="AD7" s="12" t="n">
+      <c r="AD7" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$E$3:$J$201="金６"))</f>
         <v>5</v>
       </c>
-      <c r="AE7" s="12" t="n">
+      <c r="AE7" s="13" t="n">
         <f aca="false">MIN(B7:AD7)</f>
         <v>4</v>
       </c>
-      <c r="AF7" s="12" t="n">
+      <c r="AF7" s="13" t="n">
         <f aca="false">MAX(B7:AD7)</f>
         <v>6</v>
       </c>
-      <c r="AG7" s="12" t="n">
+      <c r="AG7" s="13" t="n">
         <f aca="false">AF7-AE7</f>
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="月１"))</f>
         <v>6</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="月２"))</f>
         <v>5</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="月４"))</f>
         <v>5</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="月５"))</f>
         <v>5</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="月６"))</f>
         <v>5</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="火１"))</f>
         <v>6</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="火３"))</f>
         <v>5</v>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="火４"))</f>
         <v>6</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="火５"))</f>
         <v>5</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="火６"))</f>
         <v>5</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O8" s="12" t="n">
+      <c r="O8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="水２"))</f>
         <v>5</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="水３"))</f>
         <v>5</v>
       </c>
-      <c r="Q8" s="12" t="n">
+      <c r="Q8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="水５"))</f>
         <v>5</v>
       </c>
-      <c r="S8" s="12" t="n">
+      <c r="S8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="水６"))</f>
         <v>5</v>
       </c>
-      <c r="T8" s="12" t="n">
+      <c r="T8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="木１"))</f>
         <v>5</v>
       </c>
-      <c r="U8" s="12" t="n">
+      <c r="U8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="木２"))</f>
         <v>6</v>
       </c>
-      <c r="V8" s="12" t="n">
+      <c r="V8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="木３"))</f>
         <v>6</v>
       </c>
-      <c r="W8" s="12" t="n">
+      <c r="W8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="木４"))</f>
         <v>5</v>
       </c>
-      <c r="X8" s="12" t="n">
+      <c r="X8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y8" s="12" t="n">
+      <c r="Y8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="金１"))</f>
         <v>5</v>
       </c>
-      <c r="Z8" s="12" t="n">
+      <c r="Z8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="金２"))</f>
         <v>6</v>
       </c>
-      <c r="AA8" s="12" t="n">
+      <c r="AA8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="金３"))</f>
         <v>6</v>
       </c>
-      <c r="AB8" s="12" t="n">
+      <c r="AB8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="金４"))</f>
         <v>6</v>
       </c>
-      <c r="AC8" s="12" t="n">
+      <c r="AC8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="金５"))</f>
         <v>5</v>
       </c>
-      <c r="AD8" s="12" t="n">
+      <c r="AD8" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$E$3:$J$201="金６"))</f>
         <v>6</v>
       </c>
-      <c r="AE8" s="12" t="n">
+      <c r="AE8" s="13" t="n">
         <f aca="false">MIN(B8:AD8)</f>
         <v>4</v>
       </c>
-      <c r="AF8" s="12" t="n">
+      <c r="AF8" s="13" t="n">
         <f aca="false">MAX(B8:AD8)</f>
         <v>6</v>
       </c>
-      <c r="AG8" s="12" t="n">
+      <c r="AG8" s="13" t="n">
         <f aca="false">AF8-AE8</f>
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="月１"))</f>
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="月２"))</f>
         <v>10</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="月３"))</f>
         <v>10</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="月４"))</f>
         <v>10</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="月５"))</f>
         <v>8</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="月６"))</f>
         <v>9</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="火１"))</f>
         <v>9</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="火２"))</f>
         <v>9</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="火３"))</f>
         <v>9</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="火４"))</f>
         <v>9</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="火５"))</f>
         <v>8</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="火６"))</f>
         <v>10</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="N9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="水１"))</f>
         <v>10</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="O9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="水２"))</f>
         <v>10</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="水３"))</f>
         <v>9</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="Q9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="水４"))</f>
         <v>10</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="水５"))</f>
         <v>9</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="S9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="水６"))</f>
         <v>10</v>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="T9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="木１"))</f>
         <v>9</v>
       </c>
-      <c r="U9" s="12" t="n">
+      <c r="U9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="木２"))</f>
         <v>9</v>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="V9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="木３"))</f>
         <v>9</v>
       </c>
-      <c r="W9" s="12" t="n">
+      <c r="W9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="木４"))</f>
         <v>9</v>
       </c>
-      <c r="X9" s="12" t="n">
+      <c r="X9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="木５"))</f>
         <v>9</v>
       </c>
-      <c r="Y9" s="12" t="n">
+      <c r="Y9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="金１"))</f>
         <v>10</v>
       </c>
-      <c r="Z9" s="12" t="n">
+      <c r="Z9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="金２"))</f>
         <v>10</v>
       </c>
-      <c r="AA9" s="12" t="n">
+      <c r="AA9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="金３"))</f>
         <v>9</v>
       </c>
-      <c r="AB9" s="12" t="n">
+      <c r="AB9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="金４"))</f>
         <v>9</v>
       </c>
-      <c r="AC9" s="12" t="n">
+      <c r="AC9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="金５"))</f>
         <v>8</v>
       </c>
-      <c r="AD9" s="12" t="n">
+      <c r="AD9" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$E$3:$J$201="金６"))</f>
         <v>9</v>
       </c>
-      <c r="AE9" s="12" t="n">
+      <c r="AE9" s="13" t="n">
         <f aca="false">MIN(B9:AD9)</f>
         <v>8</v>
       </c>
-      <c r="AF9" s="12" t="n">
+      <c r="AF9" s="13" t="n">
         <f aca="false">MAX(B9:AD9)</f>
         <v>10</v>
       </c>
-      <c r="AG9" s="12" t="n">
+      <c r="AG9" s="13" t="n">
         <f aca="false">AF9-AE9</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月１"))</f>
         <v>4</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月２"))</f>
         <v>4</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月３"))</f>
         <v>4</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月４"))</f>
         <v>3</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月５"))</f>
         <v>3</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月６"))</f>
         <v>5</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火１"))</f>
         <v>4</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火２"))</f>
         <v>4</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火３"))</f>
         <v>4</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火４"))</f>
         <v>4</v>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火５"))</f>
         <v>3</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火６"))</f>
         <v>4</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O10" s="12" t="n">
+      <c r="O10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水２"))</f>
         <v>4</v>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水３"))</f>
         <v>4</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水４"))</f>
         <v>4</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水５"))</f>
         <v>3</v>
       </c>
-      <c r="S10" s="12" t="n">
+      <c r="S10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水６"))</f>
         <v>4</v>
       </c>
-      <c r="T10" s="12" t="n">
+      <c r="T10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木１"))</f>
         <v>4</v>
       </c>
-      <c r="U10" s="12" t="n">
+      <c r="U10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木２"))</f>
         <v>4</v>
       </c>
-      <c r="V10" s="12" t="n">
+      <c r="V10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木３"))</f>
         <v>4</v>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木４"))</f>
         <v>4</v>
       </c>
-      <c r="X10" s="12" t="n">
+      <c r="X10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木５"))</f>
         <v>3</v>
       </c>
-      <c r="Y10" s="12" t="n">
+      <c r="Y10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金１"))</f>
         <v>4</v>
       </c>
-      <c r="Z10" s="12" t="n">
+      <c r="Z10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金２"))</f>
         <v>4</v>
       </c>
-      <c r="AA10" s="12" t="n">
+      <c r="AA10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金３"))</f>
         <v>4</v>
       </c>
-      <c r="AB10" s="12" t="n">
+      <c r="AB10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金４"))</f>
         <v>4</v>
       </c>
-      <c r="AC10" s="12" t="n">
+      <c r="AC10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金５"))</f>
         <v>3</v>
       </c>
-      <c r="AD10" s="12" t="n">
+      <c r="AD10" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金６"))</f>
         <v>4</v>
       </c>
-      <c r="AE10" s="12" t="n">
+      <c r="AE10" s="13" t="n">
         <f aca="false">MIN(B10:AD10)</f>
         <v>3</v>
       </c>
-      <c r="AF10" s="12" t="n">
+      <c r="AF10" s="13" t="n">
         <f aca="false">MAX(B10:AD10)</f>
         <v>5</v>
       </c>
-      <c r="AG10" s="12" t="n">
+      <c r="AG10" s="13" t="n">
         <f aca="false">AF10-AE10</f>
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月１"))</f>
         <v>33</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月２"))</f>
         <v>34</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月３"))</f>
         <v>34</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月４"))</f>
         <v>33</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月５"))</f>
         <v>29</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="月６"))</f>
         <v>34</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火１"))</f>
         <v>33</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火２"))</f>
         <v>32</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火３"))</f>
         <v>33</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火４"))</f>
         <v>33</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火５"))</f>
         <v>29</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="火６"))</f>
         <v>34</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水１"))</f>
         <v>34</v>
       </c>
-      <c r="O11" s="12" t="n">
+      <c r="O11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水２"))</f>
         <v>34</v>
       </c>
-      <c r="P11" s="12" t="n">
+      <c r="P11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水３"))</f>
         <v>33</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水４"))</f>
         <v>33</v>
       </c>
-      <c r="R11" s="12" t="n">
+      <c r="R11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水５"))</f>
         <v>30</v>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="水６"))</f>
         <v>34</v>
       </c>
-      <c r="T11" s="12" t="n">
+      <c r="T11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木１"))</f>
         <v>33</v>
       </c>
-      <c r="U11" s="12" t="n">
+      <c r="U11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木２"))</f>
         <v>33</v>
       </c>
-      <c r="V11" s="12" t="n">
+      <c r="V11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木３"))</f>
         <v>34</v>
       </c>
-      <c r="W11" s="12" t="n">
+      <c r="W11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木４"))</f>
         <v>34</v>
       </c>
-      <c r="X11" s="12" t="n">
+      <c r="X11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="木５"))</f>
         <v>29</v>
       </c>
-      <c r="Y11" s="12" t="n">
+      <c r="Y11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金１"))</f>
         <v>34</v>
       </c>
-      <c r="Z11" s="12" t="n">
+      <c r="Z11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金２"))</f>
         <v>33</v>
       </c>
-      <c r="AA11" s="12" t="n">
+      <c r="AA11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金３"))</f>
         <v>33</v>
       </c>
-      <c r="AB11" s="12" t="n">
+      <c r="AB11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金４"))</f>
         <v>33</v>
       </c>
-      <c r="AC11" s="12" t="n">
+      <c r="AC11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金５"))</f>
         <v>29</v>
       </c>
-      <c r="AD11" s="12" t="n">
+      <c r="AD11" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$E$3:$J$201="金６"))</f>
         <v>34</v>
       </c>
-      <c r="AE11" s="12" t="n">
+      <c r="AE11" s="13" t="n">
         <f aca="false">MIN(B11:AD11)</f>
         <v>29</v>
       </c>
-      <c r="AF11" s="12" t="n">
+      <c r="AF11" s="13" t="n">
         <f aca="false">MAX(B11:AD11)</f>
         <v>34</v>
       </c>
-      <c r="AG11" s="12" t="n">
+      <c r="AG11" s="13" t="n">
         <f aca="false">AF11-AE11</f>
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="R14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="S14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="T14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="U14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="V14" s="11" t="s">
+      <c r="V14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W14" s="11" t="s">
+      <c r="W14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="X14" s="11" t="s">
+      <c r="X14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="Y14" s="11" t="s">
+      <c r="Y14" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="Z14" s="11" t="s">
+      <c r="Z14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AA14" s="11" t="s">
+      <c r="AA14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="AB14" s="11" t="s">
+      <c r="AB14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AC14" s="11" t="s">
+      <c r="AC14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="AD14" s="11" t="s">
+      <c r="AD14" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="AE14" s="11" t="s">
+      <c r="AE14" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="AF14" s="11" t="s">
+      <c r="AF14" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="AG14" s="11" t="s">
+      <c r="AG14" s="12" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="月１"))</f>
         <v>5</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="月２"))</f>
         <v>5</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="月４"))</f>
         <v>5</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="月５"))</f>
         <v>4</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="月６"))</f>
         <v>4</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="火１"))</f>
         <v>4</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="火３"))</f>
         <v>5</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="K15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="火４"))</f>
         <v>5</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="L15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="火５"))</f>
         <v>4</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="火６"))</f>
         <v>4</v>
       </c>
-      <c r="N15" s="12" t="n">
+      <c r="N15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="水１"))</f>
         <v>4</v>
       </c>
-      <c r="O15" s="12" t="n">
+      <c r="O15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="水２"))</f>
         <v>4</v>
       </c>
-      <c r="P15" s="12" t="n">
+      <c r="P15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="水３"))</f>
         <v>4</v>
       </c>
-      <c r="Q15" s="12" t="n">
+      <c r="Q15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R15" s="12" t="n">
+      <c r="R15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="水５"))</f>
         <v>4</v>
       </c>
-      <c r="S15" s="12" t="n">
+      <c r="S15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="水６"))</f>
         <v>4</v>
       </c>
-      <c r="T15" s="12" t="n">
+      <c r="T15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="木１"))</f>
         <v>4</v>
       </c>
-      <c r="U15" s="12" t="n">
+      <c r="U15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="木２"))</f>
         <v>5</v>
       </c>
-      <c r="V15" s="12" t="n">
+      <c r="V15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="木３"))</f>
         <v>4</v>
       </c>
-      <c r="W15" s="12" t="n">
+      <c r="W15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="木４"))</f>
         <v>4</v>
       </c>
-      <c r="X15" s="12" t="n">
+      <c r="X15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y15" s="12" t="n">
+      <c r="Y15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="金１"))</f>
         <v>4</v>
       </c>
-      <c r="Z15" s="12" t="n">
+      <c r="Z15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="金２"))</f>
         <v>4</v>
       </c>
-      <c r="AA15" s="12" t="n">
+      <c r="AA15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="金３"))</f>
         <v>5</v>
       </c>
-      <c r="AB15" s="12" t="n">
+      <c r="AB15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC15" s="12" t="n">
+      <c r="AC15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="金５"))</f>
         <v>5</v>
       </c>
-      <c r="AD15" s="12" t="n">
+      <c r="AD15" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$K$3:$P$201="金６"))</f>
         <v>5</v>
       </c>
-      <c r="AE15" s="12" t="n">
+      <c r="AE15" s="13" t="n">
         <f aca="false">MIN(B15:AD15)</f>
         <v>4</v>
       </c>
-      <c r="AF15" s="12" t="n">
+      <c r="AF15" s="13" t="n">
         <f aca="false">MAX(B15:AD15)</f>
         <v>5</v>
       </c>
-      <c r="AG15" s="12" t="n">
+      <c r="AG15" s="13" t="n">
         <f aca="false">AF15-AE15</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="月１"))</f>
         <v>4</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="月２"))</f>
         <v>4</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="月４"))</f>
         <v>4</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="月５"))</f>
         <v>4</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="月６"))</f>
         <v>5</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="火１"))</f>
         <v>5</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="火３"))</f>
         <v>4</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="火４"))</f>
         <v>4</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="L16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="火５"))</f>
         <v>4</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="火６"))</f>
         <v>5</v>
       </c>
-      <c r="N16" s="12" t="n">
+      <c r="N16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O16" s="12" t="n">
+      <c r="O16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="水２"))</f>
         <v>5</v>
       </c>
-      <c r="P16" s="12" t="n">
+      <c r="P16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="水３"))</f>
         <v>5</v>
       </c>
-      <c r="Q16" s="12" t="n">
+      <c r="Q16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R16" s="12" t="n">
+      <c r="R16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="水５"))</f>
         <v>4</v>
       </c>
-      <c r="S16" s="12" t="n">
+      <c r="S16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="水６"))</f>
         <v>5</v>
       </c>
-      <c r="T16" s="12" t="n">
+      <c r="T16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="木１"))</f>
         <v>5</v>
       </c>
-      <c r="U16" s="12" t="n">
+      <c r="U16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="木２"))</f>
         <v>5</v>
       </c>
-      <c r="V16" s="12" t="n">
+      <c r="V16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="木３"))</f>
         <v>5</v>
       </c>
-      <c r="W16" s="12" t="n">
+      <c r="W16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="木４"))</f>
         <v>5</v>
       </c>
-      <c r="X16" s="12" t="n">
+      <c r="X16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="木５"))</f>
         <v>5</v>
       </c>
-      <c r="Y16" s="12" t="n">
+      <c r="Y16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="金１"))</f>
         <v>5</v>
       </c>
-      <c r="Z16" s="12" t="n">
+      <c r="Z16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="金２"))</f>
         <v>5</v>
       </c>
-      <c r="AA16" s="12" t="n">
+      <c r="AA16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="金３"))</f>
         <v>5</v>
       </c>
-      <c r="AB16" s="12" t="n">
+      <c r="AB16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC16" s="12" t="n">
+      <c r="AC16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="金５"))</f>
         <v>4</v>
       </c>
-      <c r="AD16" s="12" t="n">
+      <c r="AD16" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$K$3:$P$201="金６"))</f>
         <v>5</v>
       </c>
-      <c r="AE16" s="12" t="n">
+      <c r="AE16" s="13" t="n">
         <f aca="false">MIN(B16:AD16)</f>
         <v>4</v>
       </c>
-      <c r="AF16" s="12" t="n">
+      <c r="AF16" s="13" t="n">
         <f aca="false">MAX(B16:AD16)</f>
         <v>5</v>
       </c>
-      <c r="AG16" s="12" t="n">
+      <c r="AG16" s="13" t="n">
         <f aca="false">AF16-AE16</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="月１"))</f>
         <v>5</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="月２"))</f>
         <v>6</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="月４"))</f>
         <v>6</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="月５"))</f>
         <v>5</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="月６"))</f>
         <v>6</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="火１"))</f>
         <v>5</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="火３"))</f>
         <v>6</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="K17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="火４"))</f>
         <v>5</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="L17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="火５"))</f>
         <v>5</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="火６"))</f>
         <v>6</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O17" s="12" t="n">
+      <c r="O17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="水２"))</f>
         <v>6</v>
       </c>
-      <c r="P17" s="12" t="n">
+      <c r="P17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="水３"))</f>
         <v>6</v>
       </c>
-      <c r="Q17" s="12" t="n">
+      <c r="Q17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R17" s="12" t="n">
+      <c r="R17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="水５"))</f>
         <v>5</v>
       </c>
-      <c r="S17" s="12" t="n">
+      <c r="S17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="水６"))</f>
         <v>6</v>
       </c>
-      <c r="T17" s="12" t="n">
+      <c r="T17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="木１"))</f>
         <v>6</v>
       </c>
-      <c r="U17" s="12" t="n">
+      <c r="U17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="木２"))</f>
         <v>5</v>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="木３"))</f>
         <v>5</v>
       </c>
-      <c r="W17" s="12" t="n">
+      <c r="W17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="木４"))</f>
         <v>6</v>
       </c>
-      <c r="X17" s="12" t="n">
+      <c r="X17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y17" s="12" t="n">
+      <c r="Y17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="金１"))</f>
         <v>6</v>
       </c>
-      <c r="Z17" s="12" t="n">
+      <c r="Z17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="金２"))</f>
         <v>5</v>
       </c>
-      <c r="AA17" s="12" t="n">
+      <c r="AA17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="金３"))</f>
         <v>5</v>
       </c>
-      <c r="AB17" s="12" t="n">
+      <c r="AB17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC17" s="12" t="n">
+      <c r="AC17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="金５"))</f>
         <v>4</v>
       </c>
-      <c r="AD17" s="12" t="n">
+      <c r="AD17" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$K$3:$P$201="金６"))</f>
         <v>5</v>
       </c>
-      <c r="AE17" s="12" t="n">
+      <c r="AE17" s="13" t="n">
         <f aca="false">MIN(B17:AD17)</f>
         <v>4</v>
       </c>
-      <c r="AF17" s="12" t="n">
+      <c r="AF17" s="13" t="n">
         <f aca="false">MAX(B17:AD17)</f>
         <v>6</v>
       </c>
-      <c r="AG17" s="12" t="n">
+      <c r="AG17" s="13" t="n">
         <f aca="false">AF17-AE17</f>
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="月１"))</f>
         <v>6</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="月２"))</f>
         <v>5</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="月４"))</f>
         <v>5</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="月５"))</f>
         <v>5</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="月６"))</f>
         <v>5</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="火１"))</f>
         <v>6</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="火３"))</f>
         <v>5</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="火４"))</f>
         <v>6</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="火５"))</f>
         <v>5</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="M18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="火６"))</f>
         <v>5</v>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="N18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O18" s="12" t="n">
+      <c r="O18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="水２"))</f>
         <v>5</v>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="水３"))</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="12" t="n">
+      <c r="Q18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R18" s="12" t="n">
+      <c r="R18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="水５"))</f>
         <v>5</v>
       </c>
-      <c r="S18" s="12" t="n">
+      <c r="S18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="水６"))</f>
         <v>5</v>
       </c>
-      <c r="T18" s="12" t="n">
+      <c r="T18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="木１"))</f>
         <v>5</v>
       </c>
-      <c r="U18" s="12" t="n">
+      <c r="U18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="木２"))</f>
         <v>6</v>
       </c>
-      <c r="V18" s="12" t="n">
+      <c r="V18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="木３"))</f>
         <v>6</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="木４"))</f>
         <v>5</v>
       </c>
-      <c r="X18" s="12" t="n">
+      <c r="X18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y18" s="12" t="n">
+      <c r="Y18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="金１"))</f>
         <v>5</v>
       </c>
-      <c r="Z18" s="12" t="n">
+      <c r="Z18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="金２"))</f>
         <v>6</v>
       </c>
-      <c r="AA18" s="12" t="n">
+      <c r="AA18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="金３"))</f>
         <v>6</v>
       </c>
-      <c r="AB18" s="12" t="n">
+      <c r="AB18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="金４"))</f>
         <v>6</v>
       </c>
-      <c r="AC18" s="12" t="n">
+      <c r="AC18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="金５"))</f>
         <v>5</v>
       </c>
-      <c r="AD18" s="12" t="n">
+      <c r="AD18" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$K$3:$P$201="金６"))</f>
         <v>6</v>
       </c>
-      <c r="AE18" s="12" t="n">
+      <c r="AE18" s="13" t="n">
         <f aca="false">MIN(B18:AD18)</f>
         <v>4</v>
       </c>
-      <c r="AF18" s="12" t="n">
+      <c r="AF18" s="13" t="n">
         <f aca="false">MAX(B18:AD18)</f>
         <v>6</v>
       </c>
-      <c r="AG18" s="12" t="n">
+      <c r="AG18" s="13" t="n">
         <f aca="false">AF18-AE18</f>
         <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="月１"))</f>
         <v>9</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="月２"))</f>
         <v>10</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="月３"))</f>
         <v>10</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="月４"))</f>
         <v>10</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="月５"))</f>
         <v>8</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="月６"))</f>
         <v>10</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="H19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="火１"))</f>
         <v>9</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="火２"))</f>
         <v>9</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="火３"))</f>
         <v>9</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="K19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="火４"))</f>
         <v>9</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="火５"))</f>
         <v>8</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="火６"))</f>
         <v>10</v>
       </c>
-      <c r="N19" s="12" t="n">
+      <c r="N19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="水１"))</f>
         <v>9</v>
       </c>
-      <c r="O19" s="12" t="n">
+      <c r="O19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="水２"))</f>
         <v>9</v>
       </c>
-      <c r="P19" s="12" t="n">
+      <c r="P19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="水３"))</f>
         <v>9</v>
       </c>
-      <c r="Q19" s="12" t="n">
+      <c r="Q19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="水４"))</f>
         <v>9</v>
       </c>
-      <c r="R19" s="12" t="n">
+      <c r="R19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="水５"))</f>
         <v>8</v>
       </c>
-      <c r="S19" s="12" t="n">
+      <c r="S19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="水６"))</f>
         <v>9</v>
       </c>
-      <c r="T19" s="12" t="n">
+      <c r="T19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="木１"))</f>
         <v>9</v>
       </c>
-      <c r="U19" s="12" t="n">
+      <c r="U19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="木２"))</f>
         <v>9</v>
       </c>
-      <c r="V19" s="12" t="n">
+      <c r="V19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="木３"))</f>
         <v>8</v>
       </c>
-      <c r="W19" s="12" t="n">
+      <c r="W19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="木４"))</f>
         <v>8</v>
       </c>
-      <c r="X19" s="12" t="n">
+      <c r="X19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="木５"))</f>
         <v>9</v>
       </c>
-      <c r="Y19" s="12" t="n">
+      <c r="Y19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="金１"))</f>
         <v>9</v>
       </c>
-      <c r="Z19" s="12" t="n">
+      <c r="Z19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="金２"))</f>
         <v>10</v>
       </c>
-      <c r="AA19" s="12" t="n">
+      <c r="AA19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="金３"))</f>
         <v>9</v>
       </c>
-      <c r="AB19" s="12" t="n">
+      <c r="AB19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="金４"))</f>
         <v>9</v>
       </c>
-      <c r="AC19" s="12" t="n">
+      <c r="AC19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="金５"))</f>
         <v>8</v>
       </c>
-      <c r="AD19" s="12" t="n">
+      <c r="AD19" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$K$3:$P$201="金６"))</f>
         <v>9</v>
       </c>
-      <c r="AE19" s="12" t="n">
+      <c r="AE19" s="13" t="n">
         <f aca="false">MIN(B19:AD19)</f>
         <v>8</v>
       </c>
-      <c r="AF19" s="12" t="n">
+      <c r="AF19" s="13" t="n">
         <f aca="false">MAX(B19:AD19)</f>
         <v>10</v>
       </c>
-      <c r="AG19" s="12" t="n">
+      <c r="AG19" s="13" t="n">
         <f aca="false">AF19-AE19</f>
         <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月１"))</f>
         <v>4</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月２"))</f>
         <v>4</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月３"))</f>
         <v>4</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月４"))</f>
         <v>3</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月５"))</f>
         <v>3</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月６"))</f>
         <v>4</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火１"))</f>
         <v>4</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火２"))</f>
         <v>4</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火３"))</f>
         <v>4</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="K20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火４"))</f>
         <v>4</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火５"))</f>
         <v>3</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火６"))</f>
         <v>4</v>
       </c>
-      <c r="N20" s="12" t="n">
+      <c r="N20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O20" s="12" t="n">
+      <c r="O20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水２"))</f>
         <v>4</v>
       </c>
-      <c r="P20" s="12" t="n">
+      <c r="P20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水３"))</f>
         <v>3</v>
       </c>
-      <c r="Q20" s="12" t="n">
+      <c r="Q20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水４"))</f>
         <v>4</v>
       </c>
-      <c r="R20" s="12" t="n">
+      <c r="R20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水５"))</f>
         <v>3</v>
       </c>
-      <c r="S20" s="12" t="n">
+      <c r="S20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水６"))</f>
         <v>4</v>
       </c>
-      <c r="T20" s="12" t="n">
+      <c r="T20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木１"))</f>
         <v>4</v>
       </c>
-      <c r="U20" s="12" t="n">
+      <c r="U20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木２"))</f>
         <v>3</v>
       </c>
-      <c r="V20" s="12" t="n">
+      <c r="V20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木３"))</f>
         <v>3</v>
       </c>
-      <c r="W20" s="12" t="n">
+      <c r="W20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木４"))</f>
         <v>4</v>
       </c>
-      <c r="X20" s="12" t="n">
+      <c r="X20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木５"))</f>
         <v>3</v>
       </c>
-      <c r="Y20" s="12" t="n">
+      <c r="Y20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金１"))</f>
         <v>4</v>
       </c>
-      <c r="Z20" s="12" t="n">
+      <c r="Z20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金２"))</f>
         <v>4</v>
       </c>
-      <c r="AA20" s="12" t="n">
+      <c r="AA20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金３"))</f>
         <v>4</v>
       </c>
-      <c r="AB20" s="12" t="n">
+      <c r="AB20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金４"))</f>
         <v>4</v>
       </c>
-      <c r="AC20" s="12" t="n">
+      <c r="AC20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金５"))</f>
         <v>3</v>
       </c>
-      <c r="AD20" s="12" t="n">
+      <c r="AD20" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金６"))</f>
         <v>4</v>
       </c>
-      <c r="AE20" s="12" t="n">
+      <c r="AE20" s="13" t="n">
         <f aca="false">MIN(B20:AD20)</f>
         <v>3</v>
       </c>
-      <c r="AF20" s="12" t="n">
+      <c r="AF20" s="13" t="n">
         <f aca="false">MAX(B20:AD20)</f>
         <v>5</v>
       </c>
-      <c r="AG20" s="12" t="n">
+      <c r="AG20" s="13" t="n">
         <f aca="false">AF20-AE20</f>
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月１"))</f>
         <v>33</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月２"))</f>
         <v>34</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月３"))</f>
         <v>34</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月４"))</f>
         <v>33</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月５"))</f>
         <v>29</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="月６"))</f>
         <v>34</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火１"))</f>
         <v>33</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火２"))</f>
         <v>33</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火３"))</f>
         <v>33</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="K21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火４"))</f>
         <v>33</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火５"))</f>
         <v>29</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="火６"))</f>
         <v>34</v>
       </c>
-      <c r="N21" s="12" t="n">
+      <c r="N21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水１"))</f>
         <v>33</v>
       </c>
-      <c r="O21" s="12" t="n">
+      <c r="O21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水２"))</f>
         <v>33</v>
       </c>
-      <c r="P21" s="12" t="n">
+      <c r="P21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水３"))</f>
         <v>32</v>
       </c>
-      <c r="Q21" s="12" t="n">
+      <c r="Q21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水４"))</f>
         <v>33</v>
       </c>
-      <c r="R21" s="12" t="n">
+      <c r="R21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水５"))</f>
         <v>29</v>
       </c>
-      <c r="S21" s="12" t="n">
+      <c r="S21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="水６"))</f>
         <v>33</v>
       </c>
-      <c r="T21" s="12" t="n">
+      <c r="T21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木１"))</f>
         <v>33</v>
       </c>
-      <c r="U21" s="12" t="n">
+      <c r="U21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木２"))</f>
         <v>33</v>
       </c>
-      <c r="V21" s="12" t="n">
+      <c r="V21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木３"))</f>
         <v>31</v>
       </c>
-      <c r="W21" s="12" t="n">
+      <c r="W21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木４"))</f>
         <v>32</v>
       </c>
-      <c r="X21" s="12" t="n">
+      <c r="X21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="木５"))</f>
         <v>29</v>
       </c>
-      <c r="Y21" s="12" t="n">
+      <c r="Y21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金１"))</f>
         <v>33</v>
       </c>
-      <c r="Z21" s="12" t="n">
+      <c r="Z21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金２"))</f>
         <v>34</v>
       </c>
-      <c r="AA21" s="12" t="n">
+      <c r="AA21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金３"))</f>
         <v>34</v>
       </c>
-      <c r="AB21" s="12" t="n">
+      <c r="AB21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金４"))</f>
         <v>34</v>
       </c>
-      <c r="AC21" s="12" t="n">
+      <c r="AC21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金５"))</f>
         <v>29</v>
       </c>
-      <c r="AD21" s="12" t="n">
+      <c r="AD21" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$K$3:$P$201="金６"))</f>
         <v>34</v>
       </c>
-      <c r="AE21" s="12" t="n">
+      <c r="AE21" s="13" t="n">
         <f aca="false">MIN(B21:AD21)</f>
         <v>29</v>
       </c>
-      <c r="AF21" s="12" t="n">
+      <c r="AF21" s="13" t="n">
         <f aca="false">MAX(B21:AD21)</f>
         <v>34</v>
       </c>
-      <c r="AG21" s="12" t="n">
+      <c r="AG21" s="13" t="n">
         <f aca="false">AF21-AE21</f>
         <v>5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="P24" s="11" t="s">
+      <c r="P24" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="Q24" s="11" t="s">
+      <c r="Q24" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R24" s="11" t="s">
+      <c r="R24" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="S24" s="11" t="s">
+      <c r="S24" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="T24" s="11" t="s">
+      <c r="T24" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="U24" s="11" t="s">
+      <c r="U24" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="V24" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W24" s="11" t="s">
+      <c r="W24" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="X24" s="11" t="s">
+      <c r="X24" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="Y24" s="11" t="s">
+      <c r="Y24" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="Z24" s="11" t="s">
+      <c r="Z24" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AA24" s="11" t="s">
+      <c r="AA24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="AB24" s="11" t="s">
+      <c r="AB24" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AC24" s="11" t="s">
+      <c r="AC24" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="AD24" s="11" t="s">
+      <c r="AD24" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="AE24" s="11" t="s">
+      <c r="AE24" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="AF24" s="11" t="s">
+      <c r="AF24" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="AG24" s="11" t="s">
+      <c r="AG24" s="12" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="月１"))</f>
         <v>4</v>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="月２"))</f>
         <v>5</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="月４"))</f>
         <v>5</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="月５"))</f>
         <v>4</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="月６"))</f>
         <v>4</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="H25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="火１"))</f>
         <v>4</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="I25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="J25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="火３"))</f>
         <v>5</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="K25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="火４"))</f>
         <v>5</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="L25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="火５"))</f>
         <v>4</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="火６"))</f>
         <v>4</v>
       </c>
-      <c r="N25" s="12" t="n">
+      <c r="N25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="水１"))</f>
         <v>4</v>
       </c>
-      <c r="O25" s="12" t="n">
+      <c r="O25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="水２"))</f>
         <v>4</v>
       </c>
-      <c r="P25" s="12" t="n">
+      <c r="P25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="水３"))</f>
         <v>4</v>
       </c>
-      <c r="Q25" s="12" t="n">
+      <c r="Q25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R25" s="12" t="n">
+      <c r="R25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="水５"))</f>
         <v>4</v>
       </c>
-      <c r="S25" s="12" t="n">
+      <c r="S25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="水６"))</f>
         <v>4</v>
       </c>
-      <c r="T25" s="12" t="n">
+      <c r="T25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="木１"))</f>
         <v>3</v>
       </c>
-      <c r="U25" s="12" t="n">
+      <c r="U25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="木２"))</f>
         <v>4</v>
       </c>
-      <c r="V25" s="12" t="n">
+      <c r="V25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="木３"))</f>
         <v>4</v>
       </c>
-      <c r="W25" s="12" t="n">
+      <c r="W25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="木４"))</f>
         <v>4</v>
       </c>
-      <c r="X25" s="12" t="n">
+      <c r="X25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y25" s="12" t="n">
+      <c r="Y25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="金１"))</f>
         <v>4</v>
       </c>
-      <c r="Z25" s="12" t="n">
+      <c r="Z25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="金２"))</f>
         <v>5</v>
       </c>
-      <c r="AA25" s="12" t="n">
+      <c r="AA25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="金３"))</f>
         <v>4</v>
       </c>
-      <c r="AB25" s="12" t="n">
+      <c r="AB25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC25" s="12" t="n">
+      <c r="AC25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="金５"))</f>
         <v>4</v>
       </c>
-      <c r="AD25" s="12" t="n">
+      <c r="AD25" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,5,19))*(授業数カウント!$Q$3:$V$201="金６"))</f>
         <v>4</v>
       </c>
-      <c r="AE25" s="12" t="n">
+      <c r="AE25" s="13" t="n">
         <f aca="false">MIN(B25:AD25)</f>
         <v>3</v>
       </c>
-      <c r="AF25" s="12" t="n">
+      <c r="AF25" s="13" t="n">
         <f aca="false">MAX(B25:AD25)</f>
         <v>5</v>
       </c>
-      <c r="AG25" s="12" t="n">
+      <c r="AG25" s="13" t="n">
         <f aca="false">AF25-AE25</f>
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="月１"))</f>
         <v>3</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="月２"))</f>
         <v>3</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="月３"))</f>
         <v>4</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="月４"))</f>
         <v>3</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="月５"))</f>
         <v>3</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="月６"))</f>
         <v>4</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="H26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="火１"))</f>
         <v>4</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="火２"))</f>
         <v>4</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="火３"))</f>
         <v>3</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="K26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="火４"))</f>
         <v>4</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="L26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="火５"))</f>
         <v>3</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="M26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="火６"))</f>
         <v>3</v>
       </c>
-      <c r="N26" s="12" t="n">
+      <c r="N26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="水１"))</f>
         <v>4</v>
       </c>
-      <c r="O26" s="12" t="n">
+      <c r="O26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="水２"))</f>
         <v>4</v>
       </c>
-      <c r="P26" s="12" t="n">
+      <c r="P26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="水３"))</f>
         <v>4</v>
       </c>
-      <c r="Q26" s="12" t="n">
+      <c r="Q26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="水４"))</f>
         <v>4</v>
       </c>
-      <c r="R26" s="12" t="n">
+      <c r="R26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="水５"))</f>
         <v>3</v>
       </c>
-      <c r="S26" s="12" t="n">
+      <c r="S26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="水６"))</f>
         <v>4</v>
       </c>
-      <c r="T26" s="12" t="n">
+      <c r="T26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="木１"))</f>
         <v>4</v>
       </c>
-      <c r="U26" s="12" t="n">
+      <c r="U26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="木２"))</f>
         <v>3</v>
       </c>
-      <c r="V26" s="12" t="n">
+      <c r="V26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="木３"))</f>
         <v>3</v>
       </c>
-      <c r="W26" s="12" t="n">
+      <c r="W26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="木４"))</f>
         <v>3</v>
       </c>
-      <c r="X26" s="12" t="n">
+      <c r="X26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="木５"))</f>
         <v>3</v>
       </c>
-      <c r="Y26" s="12" t="n">
+      <c r="Y26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="金１"))</f>
         <v>3</v>
       </c>
-      <c r="Z26" s="12" t="n">
+      <c r="Z26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="金２"))</f>
         <v>4</v>
       </c>
-      <c r="AA26" s="12" t="n">
+      <c r="AA26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="金３"))</f>
         <v>4</v>
       </c>
-      <c r="AB26" s="12" t="n">
+      <c r="AB26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="金４"))</f>
         <v>4</v>
       </c>
-      <c r="AC26" s="12" t="n">
+      <c r="AC26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="金５"))</f>
         <v>3</v>
       </c>
-      <c r="AD26" s="12" t="n">
+      <c r="AD26" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,5,20))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,6,28))*(授業数カウント!$Q$3:$V$201="金６"))</f>
         <v>4</v>
       </c>
-      <c r="AE26" s="12" t="n">
+      <c r="AE26" s="13" t="n">
         <f aca="false">MIN(B26:AD26)</f>
         <v>3</v>
       </c>
-      <c r="AF26" s="12" t="n">
+      <c r="AF26" s="13" t="n">
         <f aca="false">MAX(B26:AD26)</f>
         <v>4</v>
       </c>
-      <c r="AG26" s="12" t="n">
+      <c r="AG26" s="13" t="n">
         <f aca="false">AF26-AE26</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="月１"))</f>
         <v>5</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="月２"))</f>
         <v>6</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="月４"))</f>
         <v>6</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="月５"))</f>
         <v>4</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="月６"))</f>
         <v>6</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="H27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="火１"))</f>
         <v>5</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="I27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="J27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="火３"))</f>
         <v>6</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="K27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="火４"))</f>
         <v>5</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="L27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="火５"))</f>
         <v>5</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="M27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="火６"))</f>
         <v>6</v>
       </c>
-      <c r="N27" s="12" t="n">
+      <c r="N27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O27" s="12" t="n">
+      <c r="O27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="水２"))</f>
         <v>6</v>
       </c>
-      <c r="P27" s="12" t="n">
+      <c r="P27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="水３"))</f>
         <v>5</v>
       </c>
-      <c r="Q27" s="12" t="n">
+      <c r="Q27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R27" s="12" t="n">
+      <c r="R27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="水５"))</f>
         <v>4</v>
       </c>
-      <c r="S27" s="12" t="n">
+      <c r="S27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="水６"))</f>
         <v>6</v>
       </c>
-      <c r="T27" s="12" t="n">
+      <c r="T27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="木１"))</f>
         <v>6</v>
       </c>
-      <c r="U27" s="12" t="n">
+      <c r="U27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="木２"))</f>
         <v>5</v>
       </c>
-      <c r="V27" s="12" t="n">
+      <c r="V27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="木３"))</f>
         <v>5</v>
       </c>
-      <c r="W27" s="12" t="n">
+      <c r="W27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="木４"))</f>
         <v>5</v>
       </c>
-      <c r="X27" s="12" t="n">
+      <c r="X27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y27" s="12" t="n">
+      <c r="Y27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="金１"))</f>
         <v>6</v>
       </c>
-      <c r="Z27" s="12" t="n">
+      <c r="Z27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="金２"))</f>
         <v>5</v>
       </c>
-      <c r="AA27" s="12" t="n">
+      <c r="AA27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="金３"))</f>
         <v>5</v>
       </c>
-      <c r="AB27" s="12" t="n">
+      <c r="AB27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC27" s="12" t="n">
+      <c r="AC27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="金５"))</f>
         <v>4</v>
       </c>
-      <c r="AD27" s="12" t="n">
+      <c r="AD27" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,6,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,9,28))*(授業数カウント!$Q$3:$V$201="金６"))</f>
         <v>4</v>
       </c>
-      <c r="AE27" s="12" t="n">
+      <c r="AE27" s="13" t="n">
         <f aca="false">MIN(B27:AD27)</f>
         <v>4</v>
       </c>
-      <c r="AF27" s="12" t="n">
+      <c r="AF27" s="13" t="n">
         <f aca="false">MAX(B27:AD27)</f>
         <v>6</v>
       </c>
-      <c r="AG27" s="12" t="n">
+      <c r="AG27" s="13" t="n">
         <f aca="false">AF27-AE27</f>
         <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="月１"))</f>
         <v>5</v>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="月２"))</f>
         <v>5</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="月３"))</f>
         <v>5</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="月４"))</f>
         <v>5</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="月５"))</f>
         <v>5</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="月６"))</f>
         <v>5</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="H28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="火１"))</f>
         <v>6</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="I28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="火２"))</f>
         <v>5</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="J28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="火３"))</f>
         <v>5</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="K28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="火４"))</f>
         <v>6</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="L28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="火５"))</f>
         <v>4</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="M28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="火６"))</f>
         <v>5</v>
       </c>
-      <c r="N28" s="12" t="n">
+      <c r="N28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="水１"))</f>
         <v>5</v>
       </c>
-      <c r="O28" s="12" t="n">
+      <c r="O28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="水２"))</f>
         <v>5</v>
       </c>
-      <c r="P28" s="12" t="n">
+      <c r="P28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="水３"))</f>
         <v>5</v>
       </c>
-      <c r="Q28" s="12" t="n">
+      <c r="Q28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="水４"))</f>
         <v>5</v>
       </c>
-      <c r="R28" s="12" t="n">
+      <c r="R28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="水５"))</f>
         <v>5</v>
       </c>
-      <c r="S28" s="12" t="n">
+      <c r="S28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="水６"))</f>
         <v>5</v>
       </c>
-      <c r="T28" s="12" t="n">
+      <c r="T28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="木１"))</f>
         <v>5</v>
       </c>
-      <c r="U28" s="12" t="n">
+      <c r="U28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="木２"))</f>
         <v>6</v>
       </c>
-      <c r="V28" s="12" t="n">
+      <c r="V28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="木３"))</f>
         <v>6</v>
       </c>
-      <c r="W28" s="12" t="n">
+      <c r="W28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="木４"))</f>
         <v>5</v>
       </c>
-      <c r="X28" s="12" t="n">
+      <c r="X28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="木５"))</f>
         <v>4</v>
       </c>
-      <c r="Y28" s="12" t="n">
+      <c r="Y28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="金１"))</f>
         <v>5</v>
       </c>
-      <c r="Z28" s="12" t="n">
+      <c r="Z28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="金２"))</f>
         <v>5</v>
       </c>
-      <c r="AA28" s="12" t="n">
+      <c r="AA28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="金３"))</f>
         <v>5</v>
       </c>
-      <c r="AB28" s="12" t="n">
+      <c r="AB28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="金４"))</f>
         <v>5</v>
       </c>
-      <c r="AC28" s="12" t="n">
+      <c r="AC28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="金５"))</f>
         <v>4</v>
       </c>
-      <c r="AD28" s="12" t="n">
+      <c r="AD28" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,9,29))*(授業数カウント!$A$3:$A$201&lt;=DATE(2027,11,18))*(授業数カウント!$Q$3:$V$201="金６"))</f>
         <v>5</v>
       </c>
-      <c r="AE28" s="12" t="n">
+      <c r="AE28" s="13" t="n">
         <f aca="false">MIN(B28:AD28)</f>
         <v>4</v>
       </c>
-      <c r="AF28" s="12" t="n">
+      <c r="AF28" s="13" t="n">
         <f aca="false">MAX(B28:AD28)</f>
         <v>6</v>
       </c>
-      <c r="AG28" s="12" t="n">
+      <c r="AG28" s="13" t="n">
         <f aca="false">AF28-AE28</f>
         <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="月１"))</f>
         <v>10</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="月２"))</f>
         <v>9</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="月３"))</f>
         <v>9</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="月４"))</f>
         <v>9</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="月５"))</f>
         <v>7</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="月６"))</f>
         <v>9</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="H29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="火１"))</f>
         <v>9</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="I29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="火２"))</f>
         <v>9</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="J29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="火３"))</f>
         <v>9</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="K29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="火４"))</f>
         <v>9</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="L29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="火５"))</f>
         <v>8</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="M29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="火６"))</f>
         <v>9</v>
       </c>
-      <c r="N29" s="12" t="n">
+      <c r="N29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="水１"))</f>
         <v>9</v>
       </c>
-      <c r="O29" s="12" t="n">
+      <c r="O29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="水２"))</f>
         <v>9</v>
       </c>
-      <c r="P29" s="12" t="n">
+      <c r="P29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="水３"))</f>
         <v>9</v>
       </c>
-      <c r="Q29" s="12" t="n">
+      <c r="Q29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="水４"))</f>
         <v>9</v>
       </c>
-      <c r="R29" s="12" t="n">
+      <c r="R29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="水５"))</f>
         <v>7</v>
       </c>
-      <c r="S29" s="12" t="n">
+      <c r="S29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="水６"))</f>
         <v>9</v>
       </c>
-      <c r="T29" s="12" t="n">
+      <c r="T29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="木１"))</f>
         <v>9</v>
       </c>
-      <c r="U29" s="12" t="n">
+      <c r="U29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="木２"))</f>
         <v>10</v>
       </c>
-      <c r="V29" s="12" t="n">
+      <c r="V29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="木３"))</f>
         <v>10</v>
       </c>
-      <c r="W29" s="12" t="n">
+      <c r="W29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="木４"))</f>
         <v>9</v>
       </c>
-      <c r="X29" s="12" t="n">
+      <c r="X29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="木５"))</f>
         <v>8</v>
       </c>
-      <c r="Y29" s="12" t="n">
+      <c r="Y29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="金１"))</f>
         <v>10</v>
       </c>
-      <c r="Z29" s="12" t="n">
+      <c r="Z29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="金２"))</f>
         <v>10</v>
       </c>
-      <c r="AA29" s="12" t="n">
+      <c r="AA29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="金３"))</f>
         <v>9</v>
       </c>
-      <c r="AB29" s="12" t="n">
+      <c r="AB29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="金４"))</f>
         <v>8</v>
       </c>
-      <c r="AC29" s="12" t="n">
+      <c r="AC29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="金５"))</f>
         <v>7</v>
       </c>
-      <c r="AD29" s="12" t="n">
+      <c r="AD29" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,11,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,2,18))*(授業数カウント!$Q$3:$V$201="金６"))</f>
         <v>9</v>
       </c>
-      <c r="AE29" s="12" t="n">
+      <c r="AE29" s="13" t="n">
         <f aca="false">MIN(B29:AD29)</f>
         <v>7</v>
       </c>
-      <c r="AF29" s="12" t="n">
+      <c r="AF29" s="13" t="n">
         <f aca="false">MAX(B29:AD29)</f>
         <v>10</v>
       </c>
-      <c r="AG29" s="12" t="n">
+      <c r="AG29" s="13" t="n">
         <f aca="false">AF29-AE29</f>
         <v>3</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月１"))</f>
         <v>1</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月２"))</f>
         <v>1</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月３"))</f>
         <v>2</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月４"))</f>
         <v>2</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月５"))</f>
         <v>1</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="G30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月６"))</f>
         <v>2</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="H30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火１"))</f>
         <v>2</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="I30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火２"))</f>
         <v>2</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="J30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火３"))</f>
         <v>2</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="K30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火４"))</f>
         <v>1</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="L30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火５"))</f>
         <v>1</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="M30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火６"))</f>
         <v>2</v>
       </c>
-      <c r="N30" s="12" t="n">
+      <c r="N30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水１"))</f>
         <v>2</v>
       </c>
-      <c r="O30" s="12" t="n">
+      <c r="O30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水２"))</f>
         <v>2</v>
       </c>
-      <c r="P30" s="12" t="n">
+      <c r="P30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水３"))</f>
         <v>1</v>
       </c>
-      <c r="Q30" s="12" t="n">
+      <c r="Q30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水４"))</f>
         <v>2</v>
       </c>
-      <c r="R30" s="12" t="n">
+      <c r="R30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水５"))</f>
         <v>1</v>
       </c>
-      <c r="S30" s="12" t="n">
+      <c r="S30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水６"))</f>
         <v>1</v>
       </c>
-      <c r="T30" s="12" t="n">
+      <c r="T30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木１"))</f>
         <v>2</v>
       </c>
-      <c r="U30" s="12" t="n">
+      <c r="U30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木２"))</f>
         <v>2</v>
       </c>
-      <c r="V30" s="12" t="n">
+      <c r="V30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木３"))</f>
         <v>2</v>
       </c>
-      <c r="W30" s="12" t="n">
+      <c r="W30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木４"))</f>
         <v>1</v>
       </c>
-      <c r="X30" s="12" t="n">
+      <c r="X30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木５"))</f>
         <v>1</v>
       </c>
-      <c r="Y30" s="12" t="n">
+      <c r="Y30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金１"))</f>
         <v>1</v>
       </c>
-      <c r="Z30" s="12" t="n">
+      <c r="Z30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金２"))</f>
         <v>1</v>
       </c>
-      <c r="AA30" s="12" t="n">
+      <c r="AA30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金３"))</f>
         <v>1</v>
       </c>
-      <c r="AB30" s="12" t="n">
+      <c r="AB30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金４"))</f>
         <v>1</v>
       </c>
-      <c r="AC30" s="12" t="n">
+      <c r="AC30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金５"))</f>
         <v>2</v>
       </c>
-      <c r="AD30" s="12" t="n">
+      <c r="AD30" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2028,2,19))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金６"))</f>
         <v>2</v>
       </c>
-      <c r="AE30" s="12" t="n">
+      <c r="AE30" s="13" t="n">
         <f aca="false">MIN(B30:AD30)</f>
         <v>1</v>
       </c>
-      <c r="AF30" s="12" t="n">
+      <c r="AF30" s="13" t="n">
         <f aca="false">MAX(B30:AD30)</f>
         <v>2</v>
       </c>
-      <c r="AG30" s="12" t="n">
+      <c r="AG30" s="13" t="n">
         <f aca="false">AF30-AE30</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月１"))</f>
         <v>28</v>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月２"))</f>
         <v>29</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月３"))</f>
         <v>30</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月４"))</f>
         <v>30</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月５"))</f>
         <v>24</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="月６"))</f>
         <v>30</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="H31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火１"))</f>
         <v>30</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="I31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火２"))</f>
         <v>30</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="J31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火３"))</f>
         <v>30</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="K31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火４"))</f>
         <v>30</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="L31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火５"))</f>
         <v>25</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="M31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="火６"))</f>
         <v>29</v>
       </c>
-      <c r="N31" s="12" t="n">
+      <c r="N31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水１"))</f>
         <v>29</v>
       </c>
-      <c r="O31" s="12" t="n">
+      <c r="O31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水２"))</f>
         <v>30</v>
       </c>
-      <c r="P31" s="12" t="n">
+      <c r="P31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水３"))</f>
         <v>28</v>
       </c>
-      <c r="Q31" s="12" t="n">
+      <c r="Q31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水４"))</f>
         <v>30</v>
       </c>
-      <c r="R31" s="12" t="n">
+      <c r="R31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水５"))</f>
         <v>24</v>
       </c>
-      <c r="S31" s="12" t="n">
+      <c r="S31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="水６"))</f>
         <v>29</v>
       </c>
-      <c r="T31" s="12" t="n">
+      <c r="T31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木１"))</f>
         <v>29</v>
       </c>
-      <c r="U31" s="12" t="n">
+      <c r="U31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木２"))</f>
         <v>30</v>
       </c>
-      <c r="V31" s="12" t="n">
+      <c r="V31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木３"))</f>
         <v>30</v>
       </c>
-      <c r="W31" s="12" t="n">
+      <c r="W31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木４"))</f>
         <v>27</v>
       </c>
-      <c r="X31" s="12" t="n">
+      <c r="X31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="木５"))</f>
         <v>24</v>
       </c>
-      <c r="Y31" s="12" t="n">
+      <c r="Y31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金１"))</f>
         <v>29</v>
       </c>
-      <c r="Z31" s="12" t="n">
+      <c r="Z31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金２"))</f>
         <v>30</v>
       </c>
-      <c r="AA31" s="12" t="n">
+      <c r="AA31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金３"))</f>
         <v>28</v>
       </c>
-      <c r="AB31" s="12" t="n">
+      <c r="AB31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金４"))</f>
         <v>28</v>
       </c>
-      <c r="AC31" s="12" t="n">
+      <c r="AC31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金５"))</f>
         <v>24</v>
       </c>
-      <c r="AD31" s="12" t="n">
+      <c r="AD31" s="13" t="n">
         <f aca="false">SUMPRODUCT((授業数カウント!$A$3:$A$201&gt;=DATE(2027,4,6))*(授業数カウント!$A$3:$A$201&lt;=DATE(2028,3,24))*(授業数カウント!$Q$3:$V$201="金６"))</f>
         <v>28</v>
       </c>
-      <c r="AE31" s="12" t="n">
+      <c r="AE31" s="13" t="n">
         <f aca="false">MIN(B31:AD31)</f>
         <v>24</v>
       </c>
-      <c r="AF31" s="12" t="n">
+      <c r="AF31" s="13" t="n">
         <f aca="false">MAX(B31:AD31)</f>
         <v>30</v>
       </c>
-      <c r="AG31" s="12" t="n">
+      <c r="AG31" s="13" t="n">
         <f aca="false">AF31-AE31</f>
         <v>6</v>
       </c>
@@ -20247,7 +20817,246 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="n">
+        <v>46490</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="n">
+        <v>46507</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="n">
+        <v>46532</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>46549</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
+        <v>46577</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
+        <v>46640</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
+        <v>46664</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
+        <v>46696</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="n">
+        <v>46710</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="n">
+        <v>46736</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="n">
+        <v>46773</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="n">
+        <v>46785</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="n">
+        <v>46808</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="n">
+        <v>46829</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -20255,37 +21064,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
